--- a/artfynd/S 997-2026 artfynd.xlsx
+++ b/artfynd/S 997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136558542</v>
       </c>
       <c r="B2" t="n">
-        <v>57616</v>
+        <v>57618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136558512</v>
       </c>
       <c r="B3" t="n">
-        <v>58594</v>
+        <v>58596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
